--- a/branches/feature/fix-katheter-pce/CodeSystem-mii-cs-kardio-supplement-snomedct.xlsx
+++ b/branches/feature/fix-katheter-pce/CodeSystem-mii-cs-kardio-supplement-snomedct.xlsx
@@ -144,10 +144,10 @@
     <t>368009|Heart valve disorder|:{116676008|Associated morphology|=49755003|Morphologically abnormal structure|,363698007|Finding site|=17401000|Cardiac valve structure|},{246112005|Severity|=24484000|Severe|}</t>
   </si>
   <si>
-    <t>73544002:{116688005=260519008}</t>
-  </si>
-  <si>
-    <t>73544002|Operation on heart valve|:{116688005|Procedure approach|=260519008|Transcatheter approach|}</t>
+    <t>73544002:{260507000=103388001}</t>
+  </si>
+  <si>
+    <t>73544002|Operation on heart valve|:{260507000|Access|=103388001|Percutaneous approach - access|}</t>
   </si>
   <si>
     <t>131148009:{42752001=789750003,246112005=24484000}</t>
